--- a/data/trans_orig/IEDAD_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IEDAD_R-Edad-trans_orig.xlsx
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>176918</t>
+          <t>174392</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>215483</t>
+          <t>212913</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>185448</t>
+          <t>188174</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>224798</t>
+          <t>226172</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>374384</t>
+          <t>373291</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>427281</t>
+          <t>427089</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>112564</t>
+          <t>112728</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>143706</t>
+          <t>145480</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>125776</t>
+          <t>125746</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>159022</t>
+          <t>159656</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3177,7 +3177,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>246479</t>
+          <t>245732</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>292833</t>
+          <t>297555</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,2%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>231873</t>
+          <t>233216</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>272968</t>
+          <t>272686</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>232594</t>
+          <t>234349</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>273450</t>
+          <t>275249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>32,43%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>478858</t>
+          <t>480680</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>538407</t>
+          <t>536203</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,2%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>91204</t>
+          <t>91643</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>121881</t>
+          <t>121584</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>107083</t>
+          <t>106414</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>140216</t>
+          <t>137806</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>205937</t>
+          <t>205330</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>250011</t>
+          <t>250017</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,7 +3433,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>152255</t>
+          <t>154366</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>190566</t>
+          <t>190414</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>162362</t>
+          <t>161335</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>201066</t>
+          <t>198535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,35%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>321865</t>
+          <t>326199</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>376770</t>
+          <t>377890</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,8%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>137787</t>
+          <t>138923</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>175993</t>
+          <t>174947</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>140871</t>
+          <t>139228</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>174887</t>
+          <t>177014</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>290145</t>
+          <t>288333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>341985</t>
+          <t>342035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,7 +6284,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,81%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>215350</t>
+          <t>215093</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>255666</t>
+          <t>257090</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>30,27%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>247939</t>
+          <t>247597</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293324</t>
+          <t>289938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>475002</t>
+          <t>475753</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>534777</t>
+          <t>534210</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>129366</t>
+          <t>129570</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>165299</t>
+          <t>166261</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>23,37%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>128835</t>
+          <t>128342</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>163947</t>
+          <t>164038</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>268411</t>
+          <t>269972</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>316852</t>
+          <t>320615</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>21,63%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>155049</t>
+          <t>156443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>192500</t>
+          <t>193240</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,43%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>156425</t>
+          <t>154538</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>193690</t>
+          <t>194595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>322658</t>
+          <t>320810</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>375614</t>
+          <t>377871</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>171593</t>
+          <t>169578</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>210006</t>
+          <t>209164</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>29,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>169707</t>
+          <t>168486</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>210307</t>
+          <t>209482</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350807</t>
+          <t>350141</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>404421</t>
+          <t>407339</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,11%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>192733</t>
+          <t>191420</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>231983</t>
+          <t>230469</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>238355</t>
+          <t>236554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>279662</t>
+          <t>280704</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>438565</t>
+          <t>438129</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>497185</t>
+          <t>495088</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,16%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>115609</t>
+          <t>116930</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>149111</t>
+          <t>149315</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>108097</t>
+          <t>108183</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>142287</t>
+          <t>140319</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>233349</t>
+          <t>232145</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>278610</t>
+          <t>280910</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>248472</t>
+          <t>247240</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>322651</t>
+          <t>323452</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>48,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>277715</t>
+          <t>276995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>338660</t>
+          <t>336727</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>539835</t>
+          <t>543523</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>639610</t>
+          <t>643524</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12325,12 +12325,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>45,06%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>151147</t>
+          <t>145139</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>198210</t>
+          <t>195225</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>188530</t>
+          <t>187258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>238720</t>
+          <t>237344</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>347942</t>
+          <t>348662</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>421344</t>
+          <t>419329</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,36%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>136171</t>
+          <t>137267</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>179549</t>
+          <t>179493</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>26,95%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>162289</t>
+          <t>161554</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>204711</t>
+          <t>206013</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>26,87%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311536</t>
+          <t>311091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>371951</t>
+          <t>372772</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>46656</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71062</t>
+          <t>68830</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,12 +12594,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>49785</t>
+          <t>50215</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74241</t>
+          <t>74921</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,12 +12629,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>103482</t>
+          <t>102424</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137351</t>
+          <t>134589</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IEDAD_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IEDAD_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -1062,47 +1062,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -1175,57 +1175,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>106171</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1518,47 +1518,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1744,57 +1744,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>253205</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1974,47 +1974,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -2313,57 +2313,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>127548</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2430,47 +2430,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2882,57 +2882,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>194097</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2999,107 +2999,107 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>206049</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>186488</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>225993</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>28,51%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>25,8%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>31,27%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>286</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>194097</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>174392</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>212913</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>177313</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>214114</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>28,5%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>31,26%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>206049</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>188174</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>226172</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>31,44%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>400146</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>372097</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>428662</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>28,51%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>31,3%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>400146</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>373291</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>427089</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>28,51%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,54%</t>
         </is>
       </c>
     </row>
@@ -3112,72 +3112,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>141515</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>125138</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>160063</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>22,15%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>127548</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>112728</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>145480</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>111310</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>143820</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>18,73%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>16,55%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>21,36%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>141515</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>125746</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>159656</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>19,58%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17,4%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>245732</t>
+          <t>245578</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>297555</t>
+          <t>291671</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -3225,72 +3225,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>382</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>253756</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>231282</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>274050</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>35,11%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>32,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>37,92%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>379</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>253205</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>233216</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>272686</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>234058</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>274713</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>37,18%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>34,25%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>40,04%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>382</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>253756</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>234349</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>275249</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>35,11%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>40,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>480680</t>
+          <t>477946</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>536203</t>
+          <t>534554</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>38,08%</t>
         </is>
       </c>
     </row>
@@ -3338,72 +3338,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>121380</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>105470</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>137085</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>16,8%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>14,59%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>18,97%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>106171</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>91643</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>121584</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>91811</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>121716</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>15,59%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>13,46%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>17,85%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>121380</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>106414</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>137806</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>205330</t>
+          <t>203797</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>250017</t>
+          <t>250328</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -3451,57 +3451,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3621,7 +3621,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3632,7 +3632,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4139,47 +4139,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -4252,57 +4252,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>146761</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4595,47 +4595,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -4821,57 +4821,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>236250</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5051,47 +5051,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -5390,57 +5390,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>157043</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5507,47 +5507,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -5959,57 +5959,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>171337</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6076,72 +6076,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>179955</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>160526</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>199740</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23,88%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>21,3%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26,51%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>171337</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>154366</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>190414</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>152225</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>190894</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>24,08%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>21,7%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>26,77%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>179955</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>161335</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>198535</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>23,88%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>326199</t>
+          <t>326796</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377890</t>
+          <t>380378</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,97%</t>
         </is>
       </c>
     </row>
@@ -6189,72 +6189,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>158571</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>142087</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>180101</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>21,04%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>18,86%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>23,9%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>157043</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>138923</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>174947</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>139588</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>176461</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>22,08%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>24,59%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>158571</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>139228</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>177014</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>21,04%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18,48%</t>
+          <t>19,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>288333</t>
+          <t>290651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>342035</t>
+          <t>341392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,3%</t>
         </is>
       </c>
     </row>
@@ -6302,72 +6302,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>374</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>268991</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>248726</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>293111</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>35,7%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>38,9%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>340</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>236250</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>215093</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>257090</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>214880</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>256697</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>33,21%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>30,24%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>374</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>268991</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>247597</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>289938</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>35,7%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>32,86%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>38,48%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>475753</t>
+          <t>476136</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>534210</t>
+          <t>535474</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,55%</t>
         </is>
       </c>
     </row>
@@ -6415,107 +6415,107 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>145990</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>127691</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>166042</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>19,37%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>16,95%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>22,04%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>146761</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>129570</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>166261</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>129858</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>166159</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>20,63%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>18,21%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>145990</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>128342</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>164038</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>19,37%</t>
-        </is>
-      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>18,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
+          <t>23,36%</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr">
+        <is>
+          <t>292751</t>
+        </is>
+      </c>
+      <c r="S27" s="2" t="inlineStr">
+        <is>
+          <t>269094</t>
+        </is>
+      </c>
+      <c r="T27" s="2" t="inlineStr">
+        <is>
+          <t>318944</t>
+        </is>
+      </c>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>19,98%</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>18,37%</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
           <t>21,77%</t>
-        </is>
-      </c>
-      <c r="Q27" s="2" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="R27" s="2" t="inlineStr">
-        <is>
-          <t>292751</t>
-        </is>
-      </c>
-      <c r="S27" s="2" t="inlineStr">
-        <is>
-          <t>269972</t>
-        </is>
-      </c>
-      <c r="T27" s="2" t="inlineStr">
-        <is>
-          <t>320615</t>
-        </is>
-      </c>
-      <c r="U27" s="2" t="inlineStr">
-        <is>
-          <t>19,98%</t>
-        </is>
-      </c>
-      <c r="V27" s="2" t="inlineStr">
-        <is>
-          <t>18,43%</t>
-        </is>
-      </c>
-      <c r="W27" s="2" t="inlineStr">
-        <is>
-          <t>21,89%</t>
         </is>
       </c>
     </row>
@@ -6528,57 +6528,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1074</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>753507</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1074</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>753507</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6698,7 +6698,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6709,7 +6709,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -7216,47 +7216,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -7329,57 +7329,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>131654</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7672,47 +7672,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -7898,57 +7898,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>210517</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8128,47 +8128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
@@ -8467,57 +8467,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>188899</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8584,47 +8584,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -9036,57 +9036,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>173301</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9153,72 +9153,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>174048</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>154686</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>192025</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23,37%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>25,78%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>173301</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>156443</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>193240</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>155342</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>192943</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>24,6%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>22,21%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>27,43%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>235</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>174048</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>154538</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>194595</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>23,37%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>320810</t>
+          <t>316052</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>377871</t>
+          <t>374127</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,82%</t>
         </is>
       </c>
     </row>
@@ -9266,72 +9266,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>188572</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>168652</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>207582</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>25,32%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>22,64%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>27,87%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>188899</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>169578</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>209164</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>171134</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>207612</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>26,82%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>24,08%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,7%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>263</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>188572</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>168486</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>209482</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>25,32%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>350141</t>
+          <t>350135</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>407339</t>
+          <t>409888</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,28%</t>
         </is>
       </c>
     </row>
@@ -9379,72 +9379,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>258061</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>236597</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>276939</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>34,65%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>31,76%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>37,18%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>332</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>210517</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>191420</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>230469</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>189551</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>230845</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>29,89%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>27,18%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>32,72%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>258061</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>236554</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>280704</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>34,65%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>438129</t>
+          <t>441922</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>495088</t>
+          <t>497837</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,35%</t>
         </is>
       </c>
     </row>
@@ -9492,72 +9492,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>124164</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>107244</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>140133</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>16,67%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>18,81%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>131654</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>116930</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>149315</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>115654</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>148148</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
         <is>
           <t>18,69%</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>16,6%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>21,2%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>187</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>124164</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>108183</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>140319</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>232145</t>
+          <t>235939</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>280910</t>
+          <t>282595</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,28%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -9605,57 +9605,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -9786,7 +9786,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -10293,64 +10293,64 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>52090</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61444</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
@@ -10406,57 +10406,57 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10749,64 +10749,64 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>182554</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
@@ -10975,57 +10975,57 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>157522</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11205,64 +11205,64 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>175518</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>212490</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>—%</t>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
@@ -11544,57 +11544,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11701,7 +11701,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -11736,7 +11736,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>275457</t>
+          <t>292644</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>247240</t>
+          <t>266732</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>323452</t>
+          <t>320862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>38,06%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48,55%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>276995</t>
+          <t>235809</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>336727</t>
+          <t>278789</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>543523</t>
+          <t>513157</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>643524</t>
+          <t>582375</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>38,06%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>45,06%</t>
+          <t>43,77%</t>
         </is>
       </c>
     </row>
@@ -12343,72 +12343,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>200126</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>180037</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>222040</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>28,56%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>25,69%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>31,68%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>145139</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>195225</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>26,1%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>21,79%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>29,31%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>212490</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>187258</t>
+          <t>154322</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237344</t>
+          <t>194083</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>386378</t>
+          <t>375644</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>348662</t>
+          <t>345274</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>419329</t>
+          <t>408787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,41%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>30,72%</t>
         </is>
       </c>
     </row>
@@ -12456,72 +12456,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>157521</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>140722</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>178410</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>22,48%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>20,08%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25,46%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>137267</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>179493</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>23,91%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>20,61%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>182554</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>161554</t>
+          <t>129091</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>206013</t>
+          <t>162461</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>23,96%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>341853</t>
+          <t>303039</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>311091</t>
+          <t>277211</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>372772</t>
+          <t>327503</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>22,78%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -12569,72 +12569,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>40835</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>60719</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>5,83%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>8,66%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>45672</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68830</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>10,33%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52089</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>50215</t>
+          <t>43248</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>74921</t>
+          <t>63282</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>102424</t>
+          <t>89679</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>134589</t>
+          <t>117248</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -12682,57 +12682,57 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
